--- a/temporario/Apontamento_Clebison.xlsx
+++ b/temporario/Apontamento_Clebison.xlsx
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="M2" s="75" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="N2" s="37" t="inlineStr">
         <is>
@@ -1478,23 +1478,25 @@
       <c r="S3" s="19" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="80" t="n">
-        <v>22660</v>
+      <c r="A4" s="80" t="inlineStr">
+        <is>
+          <t>FAT26871938</t>
+        </is>
       </c>
       <c r="B4" s="81" t="inlineStr">
         <is>
-          <t>26/02260</t>
+          <t>26/02087</t>
         </is>
       </c>
       <c r="C4" s="82" t="inlineStr">
         <is>
-          <t>CATUPIRY - SANTA VITORIA</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="D4" s="83" t="n"/>
       <c r="E4" s="82" t="inlineStr">
         <is>
-          <t>8,5 + 2</t>
+          <t>2 + 2</t>
         </is>
       </c>
       <c r="F4" s="83" t="n"/>
@@ -1515,23 +1517,23 @@
     <row r="5">
       <c r="A5" s="86" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAT27649567 </t>
+          <t>FAT28080095</t>
         </is>
       </c>
       <c r="B5" s="87" t="inlineStr">
         <is>
-          <t>26/02413</t>
+          <t>26/02317</t>
         </is>
       </c>
       <c r="C5" s="76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CP KELCO BRASIL S/A.</t>
+          <t>FENIX AGRO-PECUS</t>
         </is>
       </c>
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="76" t="inlineStr">
         <is>
-          <t>17 + 1</t>
+          <t>6,3 + 1,5</t>
         </is>
       </c>
       <c r="F5" s="26" t="n"/>
@@ -1550,27 +1552,11 @@
       <c r="S5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="86" t="inlineStr">
-        <is>
-          <t>FAT27774363363</t>
-        </is>
-      </c>
-      <c r="B6" s="87" t="inlineStr">
-        <is>
-          <t>26/02418</t>
-        </is>
-      </c>
-      <c r="C6" s="76" t="inlineStr">
-        <is>
-          <t>CERAMFIX</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="45" t="n"/>
       <c r="D6" s="26" t="n"/>
-      <c r="E6" s="76" t="inlineStr">
-        <is>
-          <t>17 + 1</t>
-        </is>
-      </c>
+      <c r="E6" s="45" t="n"/>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>

--- a/temporario/Apontamento_Clebison.xlsx
+++ b/temporario/Apontamento_Clebison.xlsx
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="M2" s="75" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="N2" s="37" t="inlineStr">
         <is>
@@ -1478,25 +1478,23 @@
       <c r="S3" s="19" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="80" t="inlineStr">
-        <is>
-          <t>FAT26871938</t>
-        </is>
+      <c r="A4" s="80" t="n">
+        <v>22660</v>
       </c>
       <c r="B4" s="81" t="inlineStr">
         <is>
-          <t>26/02087</t>
+          <t>26/02260</t>
         </is>
       </c>
       <c r="C4" s="82" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CATUPIRY - SANTA VITORIA</t>
         </is>
       </c>
       <c r="D4" s="83" t="n"/>
       <c r="E4" s="82" t="inlineStr">
         <is>
-          <t>2 + 2</t>
+          <t>8,5 + 2</t>
         </is>
       </c>
       <c r="F4" s="83" t="n"/>
@@ -1517,23 +1515,23 @@
     <row r="5">
       <c r="A5" s="86" t="inlineStr">
         <is>
-          <t>FAT28080095</t>
+          <t xml:space="preserve">FAT27649567 </t>
         </is>
       </c>
       <c r="B5" s="87" t="inlineStr">
         <is>
-          <t>26/02317</t>
+          <t>26/02413</t>
         </is>
       </c>
       <c r="C5" s="76" t="inlineStr">
         <is>
-          <t>FENIX AGRO-PECUS</t>
+          <t xml:space="preserve"> CP KELCO BRASIL S/A.</t>
         </is>
       </c>
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="76" t="inlineStr">
         <is>
-          <t>6,3 + 1,5</t>
+          <t>17 + 1</t>
         </is>
       </c>
       <c r="F5" s="26" t="n"/>
@@ -1552,11 +1550,27 @@
       <c r="S5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="24" t="n"/>
-      <c r="C6" s="45" t="n"/>
+      <c r="A6" s="86" t="inlineStr">
+        <is>
+          <t>FAT27774363363</t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>26/02418</t>
+        </is>
+      </c>
+      <c r="C6" s="76" t="inlineStr">
+        <is>
+          <t>CERAMFIX</t>
+        </is>
+      </c>
       <c r="D6" s="26" t="n"/>
-      <c r="E6" s="45" t="n"/>
+      <c r="E6" s="76" t="inlineStr">
+        <is>
+          <t>17 + 1</t>
+        </is>
+      </c>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
